--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T10:41:09+00:00</t>
+    <t>2026-08-27T11:11:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:11:54+00:00</t>
+    <t>2026-08-27T11:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T11:29:36+00:00</t>
+    <t>2026-08-27T12:06:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T12:06:00+00:00</t>
+    <t>2026-08-27T15:31:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:31:43+00:00</t>
+    <t>2026-08-27T15:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T15:57:15+00:00</t>
+    <t>2026-08-28T06:12:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:12:02+00:00</t>
+    <t>2026-08-28T06:31:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:31:49+00:00</t>
+    <t>2026-08-28T06:49:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:49:57+00:00</t>
+    <t>2026-08-28T07:24:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:24:31+00:00</t>
+    <t>2026-08-28T07:40:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2015,14 +2015,14 @@
     <t>CarePlan.activity:extended.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-therapieempfehlung-kombinationstherapie|MedicationRequest|ServiceRequest)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-therapieempfehlung-kombinationstherapie|https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-therapieempfehlung-medikation|https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/StructureDefinition/mii-pr-onko-therapieempfehlung-operation)
 </t>
   </si>
   <si>
     <t>Detailed therapy recommendation - RequestGroup, MedicationRequest, or ServiceRequest</t>
   </si>
   <si>
-    <t>Reference to detailed therapy recommendations: RequestGroup for complex multi-agent protocols, MedicationRequest for specific medication orders, or ServiceRequest for therapy referrals (surgery, radiation, etc.)</t>
+    <t>Reference to detailed therapy recommendations: Therapieempfehlung Kombinationstherapie (RequestGroup) for complex multi-agent protocols, Therapieempfehlung Medikation (MedicationRequest) for specific medication orders, or Therapieempfehlung Operation (ServiceRequest) for therapy referrals (surgery, radiation, etc.)</t>
   </si>
   <si>
     <t>RequestGroup with 19.1</t>
@@ -2433,7 +2433,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="163.6796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:40:52+00:00</t>
+    <t>2026-08-28T08:03:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:03:44+00:00</t>
+    <t>2026-08-28T09:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:05:47+00:00</t>
+    <t>2026-08-28T09:25:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:25:31+00:00</t>
+    <t>2026-08-28T09:53:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:53:30+00:00</t>
+    <t>2026-08-28T10:16:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:16:47+00:00</t>
+    <t>2026-08-28T12:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:10:16+00:00</t>
+    <t>2026-08-28T12:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:26:30+00:00</t>
+    <t>2026-08-28T12:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:47:27+00:00</t>
+    <t>2026-08-28T13:10:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:10:09+00:00</t>
+    <t>2026-08-28T13:33:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:33:24+00:00</t>
+    <t>2026-08-28T13:57:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:57:18+00:00</t>
+    <t>2026-08-28T14:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:33:40+00:00</t>
+    <t>2026-08-28T14:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:57:41+00:00</t>
+    <t>2026-08-28T15:24:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:24:04+00:00</t>
+    <t>2026-08-28T15:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:48:09+00:00</t>
+    <t>2026-08-28T18:25:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T18:25:22+00:00</t>
+    <t>2026-08-28T19:18:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T19:18:26+00:00</t>
+    <t>2026-08-31T13:44:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:44:47+00:00</t>
+    <t>2026-08-31T14:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T14:28:40+00:00</t>
+    <t>2026-08-31T15:22:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:22:09+00:00</t>
+    <t>2026-09-01T08:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:53:35+00:00</t>
+    <t>2026-09-01T09:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:38:31+00:00</t>
+    <t>2026-09-01T11:08:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:08:21+00:00</t>
+    <t>2026-09-01T14:29:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:29:01+00:00</t>
+    <t>2026-09-01T19:43:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T19:43:49+00:00</t>
+    <t>2026-09-01T20:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T20:38:11+00:00</t>
+    <t>2026-09-01T21:24:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
+++ b/branches/migration/2026.0.3-template-v0.11.1/StructureDefinition-mii-pr-onko-tumorkonferenz.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T21:24:42+00:00</t>
+    <t>2026-09-01T22:10:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
